--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486970_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486970_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6207</v>
+        <v>1.7467</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0194</v>
+        <v>3.8105</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6013</v>
+        <v>-2.0638</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8443000000000001</v>
+        <v>-3.671</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-1.0345</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9157999999999999</v>
+        <v>-2.6365</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0929</v>
+        <v>0.5063</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6584</v>
+        <v>0.2438</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5656</v>
+        <v>0.2625</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9372</v>
+        <v>-4.1773</v>
       </c>
       <c r="N2" t="n">
-        <v>0.587</v>
+        <v>-1.2783</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3502</v>
+        <v>-2.899</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.045</v>
+        <v>0.987</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1122</v>
+        <v>0.1626</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1572</v>
+        <v>0.8244</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.8414</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>5.195</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3536</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5031</v>
+        <v>1.5301</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3</v>
+        <v>-0.1898</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7969000000000001</v>
+        <v>1.7199</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0589</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.117</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1759</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1689</v>
+        <v>-0.0929</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1164</v>
+        <v>-0.6584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0525</v>
+        <v>0.5656</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2278</v>
+        <v>0.9372</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9994</v>
+        <v>0.587</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2284</v>
+        <v>0.3502</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2684</v>
+        <v>-0.1356</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8909</v>
+        <v>-0.097</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3775</v>
+        <v>-0.0386</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4853</v>
+        <v>1.44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2707</v>
+        <v>0.1661</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2146</v>
+        <v>1.2739</v>
       </c>
       <c r="G4" t="n">
         <v>1.0359</v>
@@ -766,13 +766,13 @@
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1208</v>
+        <v>0.0755</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3176</v>
+        <v>0.213</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1967</v>
+        <v>-0.1374</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6982</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1561</v>
+        <v>1.0773</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0124</v>
+        <v>2.0521</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8563</v>
+        <v>-0.9747</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.671</v>
+        <v>-1.0589</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0345</v>
+        <v>0.117</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.6365</v>
+        <v>-1.1759</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5063</v>
+        <v>1.1689</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2438</v>
+        <v>1.1164</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2625</v>
+        <v>0.0525</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.1773</v>
+        <v>-2.2278</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2783</v>
+        <v>-0.9994</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.899</v>
+        <v>-1.2284</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4107</v>
+        <v>1.6427</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3964</v>
+        <v>0.8426</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6355</v>
+        <v>0.643</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0319</v>
+        <v>0.1996</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8414</v>
+        <v>-0.3491</v>
       </c>
       <c r="W5" t="n">
-        <v>5.195</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3536</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6541</v>
+        <v>0.7792</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0072</v>
+        <v>2.0731</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3532</v>
+        <v>-1.2939</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9109</v>
@@ -922,13 +922,13 @@
         <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0704</v>
+        <v>0.1956</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4221</v>
+        <v>0.4879</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3516</v>
+        <v>-0.2924</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3536</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2903</v>
+        <v>-0.5745</v>
       </c>
       <c r="E7" t="n">
-        <v>1.297</v>
+        <v>0.9832</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5873</v>
+        <v>-1.5577</v>
       </c>
       <c r="G7" t="n">
         <v>0.7915</v>
@@ -1000,13 +1000,13 @@
         <v>0.4107</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0352</v>
+        <v>-0.249</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4339</v>
+        <v>0.1201</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3986</v>
+        <v>-0.369</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5277</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8134</v>
+        <v>-0.8726</v>
       </c>
       <c r="E8" t="n">
         <v>0.8047</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.618</v>
+        <v>-1.6773</v>
       </c>
       <c r="G8" t="n">
         <v>0.7186</v>
@@ -1078,13 +1078,13 @@
         <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3185</v>
+        <v>-0.3777</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3952</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0175</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4189</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3489</v>
+        <v>-1.9919</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6922</v>
+        <v>-0.9852</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0411</v>
+        <v>-1.0067</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4384</v>
+        <v>-3.8653</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0941</v>
+        <v>0.8368</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.3442</v>
+        <v>-4.7022</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3738</v>
+        <v>-1.7379</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6263</v>
+        <v>1.2492</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0001</v>
+        <v>-2.9871</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0646</v>
+        <v>-2.1275</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7204</v>
+        <v>-0.4124</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3441</v>
+        <v>-1.7151</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4431</v>
+        <v>-0.8078</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3248</v>
+        <v>-0.2288</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1183</v>
+        <v>-0.579</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2357</v>
+        <v>1.6546</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7679</v>
+        <v>2.0082</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5322</v>
+        <v>-0.3536</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9399</v>
+        <v>-2.4385</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9925</v>
+        <v>-0.2492</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9474</v>
+        <v>-2.1893</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8653</v>
+        <v>-3.4384</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8368</v>
+        <v>-0.0941</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.7022</v>
+        <v>-3.3442</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7379</v>
+        <v>-1.3738</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2492</v>
+        <v>0.6263</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9871</v>
+        <v>-2.0001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1275</v>
+        <v>-2.0646</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4124</v>
+        <v>-0.7204</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7151</v>
+        <v>-1.3441</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7559</v>
+        <v>0.3535</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2361</v>
+        <v>0.3833</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.0299</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6546</v>
+        <v>0.2357</v>
       </c>
       <c r="W10" t="n">
-        <v>2.0082</v>
+        <v>1.7679</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3536</v>
+        <v>-1.5322</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7722</v>
+        <v>-3.3036</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0548</v>
+        <v>-0.6751</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7174</v>
+        <v>-2.6285</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6014</v>
@@ -1312,13 +1312,13 @@
         <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.46</v>
+        <v>0.0086</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.407</v>
+        <v>-0.0273</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0529</v>
+        <v>0.036</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3536</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8743</v>
+        <v>-3.6825</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2055</v>
+        <v>-3.3101</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6688</v>
+        <v>-0.3724</v>
       </c>
       <c r="G12" t="n">
         <v>-4.4352</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0968</v>
+        <v>0.2886</v>
       </c>
       <c r="T12" t="n">
-        <v>0.12</v>
+        <v>0.0154</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0232</v>
+        <v>0.2732</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1786</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6197</v>
+        <v>-6.2903</v>
       </c>
       <c r="E13" t="n">
-        <v>4.150800000000001</v>
+        <v>4.4803</v>
       </c>
       <c r="F13" t="n">
         <v>-10.7705</v>
@@ -1444,7 +1444,7 @@
         <v>-1.4434</v>
       </c>
       <c r="K13" t="n">
-        <v>6.361600000000001</v>
+        <v>6.3616</v>
       </c>
       <c r="L13" t="n">
         <v>-7.8048</v>
@@ -1468,22 +1468,22 @@
         <v>14.3738</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8517000000000001</v>
+        <v>1.1813</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9477000000000001</v>
+        <v>1.277</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09539999999999987</v>
+        <v>-0.09560000000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8520000000000005</v>
+        <v>0.8520000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.753300000000001</v>
+        <v>8.753299999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.901300000000001</v>
+        <v>-7.9013</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1869</v>
+        <v>4.7517</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0756</v>
+        <v>4.5986</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1114</v>
+        <v>0.1532</v>
       </c>
       <c r="G14" t="n">
         <v>4.2282</v>
@@ -1546,13 +1546,13 @@
         <v>0.4107</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8359</v>
+        <v>-0.2711</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7169</v>
+        <v>-0.1939</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1191</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.5893</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4165</v>
+        <v>3.2575</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0299</v>
+        <v>2.3493</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6133999999999999</v>
+        <v>0.9082</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6691</v>
+        <v>5.7181</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8401999999999999</v>
+        <v>-0.2045</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8288</v>
+        <v>5.9225</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4868</v>
+        <v>4.6431</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1714</v>
+        <v>0.5129</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3154</v>
+        <v>4.1301</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1823</v>
+        <v>1.075</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3311</v>
+        <v>-0.7174</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5134</v>
+        <v>1.7924</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0267</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1848</v>
+        <v>0.0117</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0072</v>
+        <v>-0.0351</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1776</v>
+        <v>0.0468</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5893</v>
+        <v>-0.8295</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1786</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2909</v>
+        <v>2.9736</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4529</v>
+        <v>3.5068</v>
       </c>
       <c r="F16" t="n">
-        <v>1.838</v>
+        <v>-0.5332</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8097</v>
+        <v>2.6691</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1298</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9395</v>
+        <v>1.8288</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2486</v>
+        <v>2.4868</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3275</v>
+        <v>1.1714</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0789</v>
+        <v>1.3154</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0582</v>
+        <v>0.1823</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1977</v>
+        <v>-0.3311</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8606</v>
+        <v>0.5134</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8481</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R16" t="n">
         <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>3.74</v>
+        <v>0.742</v>
       </c>
       <c r="T16" t="n">
-        <v>2.336</v>
+        <v>0.4842</v>
       </c>
       <c r="U16" t="n">
-        <v>1.404</v>
+        <v>0.2578</v>
       </c>
       <c r="V16" t="n">
         <v>0.5893</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4189</v>
+        <v>1.7679</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8295</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4067</v>
+        <v>1.1656</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0354</v>
+        <v>-0.0115</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3712</v>
+        <v>1.1771</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7181</v>
+        <v>0.8097</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2045</v>
+        <v>-0.1298</v>
       </c>
       <c r="I17" t="n">
-        <v>5.9225</v>
+        <v>0.9395</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6431</v>
+        <v>-0.2486</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5129</v>
+        <v>-0.3275</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1301</v>
+        <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>1.075</v>
+        <v>1.0582</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7174</v>
+        <v>0.1977</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7924</v>
+        <v>0.8606</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6427</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2588</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8391</v>
+        <v>1.6147</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3489</v>
+        <v>0.8716</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4902</v>
+        <v>0.7431</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8295</v>
+        <v>0.5893</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X17" t="n">
         <v>-0.8295</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BONO SOLER</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3523</v>
+        <v>0.9111</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02</v>
+        <v>2.4519</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3724</v>
+        <v>-1.5408</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4954</v>
+        <v>1.8468</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0034</v>
+        <v>-1.6289</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.492</v>
+        <v>3.4757</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4616</v>
+        <v>2.5558</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0779</v>
+        <v>0.1752</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5395</v>
+        <v>2.3806</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0338</v>
+        <v>-0.709</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0813</v>
+        <v>-1.8041</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0475</v>
+        <v>1.0951</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6424</v>
+        <v>-0.0794</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4416</v>
+        <v>-0.0505</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2008</v>
+        <v>-0.0289</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>P. BONO SOLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5151</v>
+        <v>0.2582</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7196</v>
+        <v>-0.3338</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2347</v>
+        <v>0.592</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8468</v>
+        <v>-0.4954</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6289</v>
+        <v>-0.0034</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4757</v>
+        <v>-0.492</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5558</v>
+        <v>-0.4616</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1752</v>
+        <v>0.0779</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3806</v>
+        <v>-0.5395</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.709</v>
+        <v>-0.0338</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8041</v>
+        <v>-0.0813</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0951</v>
+        <v>0.0475</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5055</v>
+        <v>0.5482</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7827</v>
+        <v>0.1278</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7228</v>
+        <v>0.4204</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5976</v>
+        <v>-0.0454</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.713</v>
+        <v>1.2485</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1154</v>
+        <v>-1.2939</v>
       </c>
       <c r="G20" t="n">
-        <v>1.379</v>
+        <v>4.5538</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7655999999999999</v>
+        <v>1.9755</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6133999999999999</v>
+        <v>2.5783</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5071</v>
+        <v>4.1424</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1519</v>
+        <v>2.4722</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3552</v>
+        <v>1.6702</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1281</v>
+        <v>0.4114</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3863</v>
+        <v>-0.4967</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2582</v>
+        <v>0.9081</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0534</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2588</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.3671</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0386</v>
+        <v>-0.4031</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0381</v>
+        <v>0.036</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1036</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9347</v>
+        <v>-0.9222</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0383</v>
+        <v>0.3351</v>
       </c>
       <c r="G21" t="n">
-        <v>4.5538</v>
+        <v>1.379</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9755</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5783</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1424</v>
+        <v>1.5071</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4722</v>
+        <v>1.1519</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6702</v>
+        <v>0.3552</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4114</v>
+        <v>-0.1281</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4967</v>
+        <v>-0.3863</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9081</v>
+        <v>0.2582</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4641</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0801</v>
+        <v>-2.2588</v>
       </c>
       <c r="R21" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4254</v>
+        <v>0.0872</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7169</v>
+        <v>-0.1706</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7085</v>
+        <v>0.2578</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1585</v>
+        <v>-0.7506</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4193</v>
+        <v>-1.2101</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2608</v>
+        <v>0.4595</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5944</v>
@@ -2170,13 +2170,13 @@
         <v>0.2053</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5765</v>
+        <v>-0.1685</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3875</v>
+        <v>-0.1783</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.189</v>
+        <v>0.0098</v>
       </c>
       <c r="V22" t="n">
         <v>0.8070000000000001</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6819</v>
+        <v>-0.9831</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.9929</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7679</v>
+        <v>0.0098</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3104</v>
+        <v>-0.2136</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1947</v>
+        <v>-1.729</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1157</v>
+        <v>1.5154</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.8541</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.0663</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3104</v>
+        <v>0.6405</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1947</v>
+        <v>-0.9412</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1157</v>
+        <v>1.5817</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3448</v>
+        <v>0.0252</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0659</v>
+        <v>-0.2907</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2789</v>
+        <v>0.3159</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W23" t="n">
         <v>1.1786</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1786</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9768</v>
+        <v>-1.5424</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4113</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5655</v>
+        <v>-1.6285</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2136</v>
+        <v>-0.3104</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.729</v>
+        <v>-0.1947</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5154</v>
+        <v>-0.1157</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8541</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0663</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6405</v>
+        <v>-0.3104</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9412</v>
+        <v>-0.1947</v>
       </c>
       <c r="O24" t="n">
-        <v>1.5817</v>
+        <v>-0.1157</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9686</v>
+        <v>-0.2053</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7091</v>
+        <v>-0.0659</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2594</v>
+        <v>-0.1395</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>1.1786</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7679</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.619799999999997</v>
+        <v>9.408999999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>10.7705</v>
+        <v>10.7706</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.150600000000001</v>
+        <v>-1.3615</v>
       </c>
       <c r="G25" t="n">
         <v>18.5909</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3797</v>
+        <v>-1.379700000000001</v>
       </c>
       <c r="I25" t="n">
         <v>19.9704</v>
@@ -2392,7 +2392,7 @@
         <v>-6.3616</v>
       </c>
       <c r="O25" t="n">
-        <v>7.8049</v>
+        <v>7.804900000000002</v>
       </c>
       <c r="P25" t="n">
         <v>-10.2671</v>
@@ -2404,13 +2404,13 @@
         <v>4.1066</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8518</v>
+        <v>1.9376</v>
       </c>
       <c r="T25" t="n">
-        <v>0.09550000000000014</v>
+        <v>0.09550000000000027</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9474000000000002</v>
+        <v>1.8419</v>
       </c>
       <c r="V25" t="n">
         <v>-0.8520000000000001</v>
